--- a/data/trans_orig/P04B1_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277350</t>
+          <t>278168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296277</t>
+          <t>296785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248045</t>
+          <t>247145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>266021</t>
+          <t>265957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>532960</t>
+          <t>531059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>558588</t>
+          <t>559263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34093</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41590</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42489</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68117</t>
+          <t>70018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>432147</t>
+          <t>432760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>471362</t>
+          <t>471482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>415675</t>
+          <t>415007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447346</t>
+          <t>446711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>857951</t>
+          <t>860734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>908571</t>
+          <t>909758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47028</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86243</t>
+          <t>85630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67623</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99294</t>
+          <t>99962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124788</t>
+          <t>123601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175408</t>
+          <t>172625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246187</t>
+          <t>246521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272510</t>
+          <t>272585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276860</t>
+          <t>276420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300289</t>
+          <t>299889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>531723</t>
+          <t>532876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566371</t>
+          <t>565608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69863</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>49239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72268</t>
+          <t>72708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98807</t>
+          <t>99570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133455</t>
+          <t>132302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>228803</t>
+          <t>227294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262611</t>
+          <t>262555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>363421</t>
+          <t>360123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>426613</t>
+          <t>424015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>603760</t>
+          <t>606264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>673626</t>
+          <t>675086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49946</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83754</t>
+          <t>85263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48943</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>115433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114487</t>
+          <t>113027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184353</t>
+          <t>181849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>109828</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132768</t>
+          <t>131884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201530</t>
+          <t>200894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>234829</t>
+          <t>235546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>316607</t>
+          <t>319109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366283</t>
+          <t>370169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44628</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66924</t>
+          <t>67568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>57885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69892</t>
+          <t>66006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119568</t>
+          <t>117066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>229302</t>
+          <t>227051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>247348</t>
+          <t>246494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218753</t>
+          <t>219631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>235520</t>
+          <t>236006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>452614</t>
+          <t>454032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>476856</t>
+          <t>478458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21421</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>47367</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73211</t>
+          <t>71793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458098</t>
+          <t>458081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>504203</t>
+          <t>502992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>583619</t>
+          <t>583287</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>751615</t>
+          <t>746276</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1068555</t>
+          <t>1070824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1261502</t>
+          <t>1268156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117006</t>
+          <t>118217</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163111</t>
+          <t>163128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>90467</t>
+          <t>95806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258463</t>
+          <t>258795</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201788</t>
+          <t>195134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>394735</t>
+          <t>392466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168073</t>
+          <t>167599</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>675962</t>
+          <t>680920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108173</t>
+          <t>108998</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147228</t>
+          <t>145798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>288195</t>
+          <t>288897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>931799</t>
+          <t>944397</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>252758</t>
+          <t>247800</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>760647</t>
+          <t>761121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>570503</t>
+          <t>571933</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>609558</t>
+          <t>608733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>714653</t>
+          <t>702055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1358257</t>
+          <t>1357555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2369539</t>
+          <t>2372691</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2678590</t>
+          <t>2678784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2497834</t>
+          <t>2488685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2806501</t>
+          <t>2800898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4908917</t>
+          <t>4909939</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5325501</t>
+          <t>5309435</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>775944</t>
+          <t>775750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1084995</t>
+          <t>1081843</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>898434</t>
+          <t>904037</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1207101</t>
+          <t>1216250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1833968</t>
+          <t>1850034</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2250552</t>
+          <t>2249530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>288718</t>
+          <t>293939</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278168</t>
+          <t>284014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296785</t>
+          <t>302015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>258000</t>
+          <t>280572</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247145</t>
+          <t>269841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265957</t>
+          <t>288576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>546717</t>
+          <t>574511</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531059</t>
+          <t>559543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>559263</t>
+          <t>586630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>34831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31635</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>46220</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54360</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41814</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70018</t>
+          <t>75363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>454935</t>
+          <t>464891</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>432760</t>
+          <t>444100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>471482</t>
+          <t>481614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>431686</t>
+          <t>459192</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>415007</t>
+          <t>442397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446711</t>
+          <t>474462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>886621</t>
+          <t>924083</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>860734</t>
+          <t>901213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>909758</t>
+          <t>948403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63455</t>
+          <t>65756</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>49033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85630</t>
+          <t>86547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>83283</t>
+          <t>87302</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99962</t>
+          <t>104097</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>153058</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123601</t>
+          <t>128738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172625</t>
+          <t>175928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>260434</t>
+          <t>258533</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246521</t>
+          <t>244396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272585</t>
+          <t>270115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>288969</t>
+          <t>293915</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276420</t>
+          <t>281640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299889</t>
+          <t>305987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>549404</t>
+          <t>552449</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>532876</t>
+          <t>534540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>565608</t>
+          <t>568695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>57460</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>45878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60159</t>
+          <t>62466</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>50394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72708</t>
+          <t>74741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>115774</t>
+          <t>119926</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99570</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132302</t>
+          <t>137835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>247665</t>
+          <t>298567</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227294</t>
+          <t>276317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262555</t>
+          <t>316644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>388927</t>
+          <t>320798</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>360123</t>
+          <t>301559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>424015</t>
+          <t>337453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>636591</t>
+          <t>619365</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>606264</t>
+          <t>588560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>675086</t>
+          <t>643122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64892</t>
+          <t>74578</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85263</t>
+          <t>96828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86629</t>
+          <t>100195</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>83540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115433</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>151522</t>
+          <t>174773</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113027</t>
+          <t>151016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>181849</t>
+          <t>205578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>122162</t>
+          <t>136850</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109828</t>
+          <t>124119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131884</t>
+          <t>147874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>215504</t>
+          <t>178737</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200894</t>
+          <t>167633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>235546</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>337666</t>
+          <t>315586</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>319109</t>
+          <t>299309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>370169</t>
+          <t>329415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55234</t>
+          <t>67353</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>56329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67568</t>
+          <t>80084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43275</t>
+          <t>50181</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>42157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57885</t>
+          <t>61285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>98509</t>
+          <t>117534</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66006</t>
+          <t>103705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117066</t>
+          <t>133811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>177396</t>
+          <t>204203</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177396</t>
+          <t>204203</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177396</t>
+          <t>204203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>436175</t>
+          <t>433120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>436175</t>
+          <t>433120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>436175</t>
+          <t>433120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238592</t>
+          <t>234373</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>227051</t>
+          <t>223414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>246494</t>
+          <t>243628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>228203</t>
+          <t>233473</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>219631</t>
+          <t>224297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236006</t>
+          <t>240829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>466795</t>
+          <t>467847</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>454032</t>
+          <t>454160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>478458</t>
+          <t>477990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>35496</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41718</t>
+          <t>46455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37425</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47367</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71793</t>
+          <t>79460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>482309</t>
+          <t>549884</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458081</t>
+          <t>524015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>502992</t>
+          <t>574249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>653159</t>
+          <t>532575</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>583287</t>
+          <t>507474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>746276</t>
+          <t>553608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1135467</t>
+          <t>1082459</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1070824</t>
+          <t>1048353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1268156</t>
+          <t>1118337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>138900</t>
+          <t>163894</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118217</t>
+          <t>139529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163128</t>
+          <t>189763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188923</t>
+          <t>231363</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95806</t>
+          <t>210330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258795</t>
+          <t>256464</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>327823</t>
+          <t>395257</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195134</t>
+          <t>359379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>392466</t>
+          <t>429363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621209</t>
+          <t>713778</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621209</t>
+          <t>713778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621209</t>
+          <t>713778</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>842082</t>
+          <t>763938</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>842082</t>
+          <t>763938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>842082</t>
+          <t>763938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1463290</t>
+          <t>1477716</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1463290</t>
+          <t>1477716</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1463290</t>
+          <t>1477716</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>373247</t>
+          <t>146055</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>167599</t>
+          <t>124262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>680920</t>
+          <t>171344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>125259</t>
+          <t>139787</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108998</t>
+          <t>121239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145798</t>
+          <t>162212</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>498506</t>
+          <t>285841</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>288897</t>
+          <t>255328</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>944397</t>
+          <t>318143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>555473</t>
+          <t>652017</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>247800</t>
+          <t>626728</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761121</t>
+          <t>673810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>592472</t>
+          <t>691544</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>571933</t>
+          <t>669119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>608733</t>
+          <t>710092</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1147946</t>
+          <t>1343562</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>702055</t>
+          <t>1311260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1357555</t>
+          <t>1374075</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2468061</t>
+          <t>2383093</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2372691</t>
+          <t>2327305</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2678784</t>
+          <t>2444983</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2589706</t>
+          <t>2439047</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2488685</t>
+          <t>2385894</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2800898</t>
+          <t>2493646</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5057767</t>
+          <t>4822141</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4909939</t>
+          <t>4744488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5309435</t>
+          <t>4899166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>986473</t>
+          <t>1141460</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>775750</t>
+          <t>1079570</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1081843</t>
+          <t>1197248</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1115229</t>
+          <t>1288820</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>904037</t>
+          <t>1234221</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1216250</t>
+          <t>1341973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2101702</t>
+          <t>2430279</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1850034</t>
+          <t>2353254</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2249530</t>
+          <t>2507932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
